--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="141">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240329120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -222,7 +222,7 @@
     <t>331</t>
   </si>
   <si>
-    <t>Secrétaire médicale</t>
+    <t>Secrétaire assistante médico-administrative</t>
   </si>
   <si>
     <t>332</t>
@@ -247,6 +247,186 @@
   </si>
   <si>
     <t>Gestionnaire alertes et urgences sanitaires</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans l'accueil et l'orientation des personnes</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la logistique</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans l'hôtellerie et la restauration</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction de la qualité, hygiène, sécurité et environnement</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des systèmes d'information</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des finances et comptabilité</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction de la communication</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des ressources humaines</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des affaires médicales</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans le social, éducatif, psychologie et culturel</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Etudiant - aide-soignant</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>Etudiant - auxiliaire de puériculture</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Etudiant - masseur-kinésithérapeute</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Externe en médecine</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Externe en odontologie</t>
+  </si>
+  <si>
+    <t>356</t>
+  </si>
+  <si>
+    <t>Externe en maïeutique</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Externe en pharmacie</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>Autre étudiant</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Directeur d'établissement</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>Brancardier</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Educateur en activité physique adaptée</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Technicien d'informations médicales</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Attaché de recherche clinique</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>Praticien A Diplôme Hors Union Européenne (PADHUE)</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Gestionnaire admissions / frais de séjour / traitement externe</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Archiviste</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Surveillant de nuit</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Animateur</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>Biologiste médical non-médecin</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Opérateur de Soins Non Programmés</t>
   </si>
   <si>
     <t/>
@@ -525,7 +705,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -737,15 +917,255 @@
         <v>78</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
